--- a/BEng/EEE6011/Machines Lab Framework 1.1 w Shunt Series Sample.xlsx
+++ b/BEng/EEE6011/Machines Lab Framework 1.1 w Shunt Series Sample.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akbar\Cloud-Drive_maa32ocd@bolton.ac.uk\School Work\L6 BEng EEE\Semester 2\EEE6011 Machines and Sensors\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akbar\Cloud-Drive_maa32ocd@bolton.ac.uk\Hobby Projects\GitHub Repos\University\Mechatronics\BEng\EEE6011\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C827C1D0-108D-4940-B2CE-CED0627C7F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F47C747-ED4D-420A-8777-3F6AB187227B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="19296" activeTab="2" xr2:uid="{AFB607F1-B90B-41C3-8DE7-CC5370CAC2B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="19416" xr2:uid="{AFB607F1-B90B-41C3-8DE7-CC5370CAC2B8}"/>
   </bookViews>
   <sheets>
     <sheet name="FrameWork" sheetId="6" r:id="rId1"/>
-    <sheet name="Shunt" sheetId="5" r:id="rId2"/>
-    <sheet name="Series" sheetId="4" r:id="rId3"/>
+    <sheet name="Series" sheetId="4" r:id="rId2"/>
+    <sheet name="Shunt" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -889,6 +889,21 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -906,6 +921,42 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -916,39 +967,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -957,24 +975,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1002,1076 +1002,24 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Armature Current vs</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Shaft Torque</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Shunt!$I$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Shaft Torque</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Shunt!$B$11:$B$20</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.86</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.97</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.1000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.38</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.61</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Shunt!$I$11:$I$20</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>9.4764600000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.17407845000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.28738395</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.42232049999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.59021865000000018</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.80858924999999993</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.99502830000000009</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.1794072500000001</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.3823270999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1D9A-4C96-8CC2-F9FC6ABD1A11}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="2029529936"/>
-        <c:axId val="2029532336"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="2029529936"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Torque</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-GB" baseline="0"/>
-                  <a:t> (Nm)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-GB"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2029532336"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="2029532336"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB"/>
-                  <a:t>Current (A)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2029529936"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>861391</xdr:colOff>
+      <xdr:colOff>898493</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>8283</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>985216</xdr:colOff>
+      <xdr:colOff>948113</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>151143</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="University of Bolton | Study Overseas | Study UK | Study Abroad">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72D8BC61-13C0-4807-908B-EC33224C3EDD}"/>
@@ -2091,14 +1039,12 @@
           </a:extLst>
         </a:blip>
         <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13320091" y="8283"/>
-          <a:ext cx="1162050" cy="342885"/>
+          <a:off x="13700093" y="8283"/>
+          <a:ext cx="1116420" cy="333360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2125,22 +1071,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>861391</xdr:colOff>
+      <xdr:colOff>900694</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>8283</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>987756</xdr:colOff>
+      <xdr:colOff>945913</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>151143</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="University of Bolton | Study Overseas | Study UK | Study Abroad">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8805902F-0DBA-4423-9F2F-92A1181B9363}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A752FD6-820F-4CD6-AA03-ADB4E388DD68}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2157,282 +1103,12 @@
           </a:extLst>
         </a:blip>
         <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="13662991" y="8283"/>
-          <a:ext cx="1190625" cy="333360"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>281668</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76744</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>91168</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>139337</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{091F8412-DB00-4976-86C2-3C7600F9BDA6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>555104</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>82502</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>342852</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>1354</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="Output image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32F3EA6A-D59D-BC0E-A9EA-870F8BF7E2FF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="16067247" y="8178752"/>
-          <a:ext cx="2645248" cy="1821446"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>19319</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>182384</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>452684</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>1756</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="Output image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7B0B52D-9FB1-0369-8849-98570BB62EE2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="22049283" y="8278634"/>
-          <a:ext cx="2828222" cy="1904846"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>315230</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>147765</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>465488</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>65259</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8" descr="Output image">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAC0E54C-EA37-EE30-7D6A-97313D69744E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="18684873" y="8053515"/>
-          <a:ext cx="3225472" cy="2203494"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>312964</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>153082</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>449036</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>160746</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13C56584-2BC8-52D1-82CD-26CE820913A0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="312964" y="5582332"/>
-          <a:ext cx="5306786" cy="3436664"/>
+          <a:off x="13702294" y="8283"/>
+          <a:ext cx="1112019" cy="332046"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2454,325 +1130,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>68036</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>68036</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>312965</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>136696</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3D21546-12EE-544F-5F11-554B453A5161}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="68036" y="9116786"/>
-          <a:ext cx="5415643" cy="3497660"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>27215</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>462642</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>132797</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{940D857F-4C4B-E054-2D54-B5321EE4CFDE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5551714" y="9266465"/>
-          <a:ext cx="5252357" cy="3344082"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>631903</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>167268</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>557562</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>78727</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D890A11-7872-D678-9967-F1AA3B3C9338}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="11225562" y="8716536"/>
-          <a:ext cx="4163122" cy="2699264"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>283028</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>65314</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>598714</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>43410</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2277352C-5779-7812-CA33-1421885C0995}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="283028" y="12540343"/>
-          <a:ext cx="5649686" cy="3679238"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>861391</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>8283</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>985216</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>151143</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="University of Bolton | Study Overseas | Study UK | Study Abroad">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A752FD6-820F-4CD6-AA03-ADB4E388DD68}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="13285304" y="8283"/>
-          <a:ext cx="1159151" cy="341643"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>233082</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>152401</xdr:rowOff>
+      <xdr:rowOff>84083</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>498054</xdr:colOff>
+      <xdr:colOff>518522</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>8965</xdr:rowOff>
+      <xdr:rowOff>105102</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2802,8 +1168,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="233082" y="5235389"/>
-          <a:ext cx="3465372" cy="2187388"/>
+          <a:off x="0" y="5270938"/>
+          <a:ext cx="3718922" cy="2412123"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2825,22 +1191,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>279722</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>77164</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>105238</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>353688</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>173620</xdr:rowOff>
+      <xdr:colOff>532590</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>131379</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="8" name="Picture 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{569D3F5A-7B80-63B9-914A-B0D68DF0B8B8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F816F09D-06B3-F3D7-A37A-227A759A2A5D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2863,8 +1229,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="279722" y="7841848"/>
-          <a:ext cx="3285941" cy="2112380"/>
+          <a:off x="0" y="12649335"/>
+          <a:ext cx="3732990" cy="2417244"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2886,22 +1252,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>559443</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>125393</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>35285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>513377</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>144685</xdr:rowOff>
+      <xdr:colOff>525516</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>16726</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D6A7180-E9F7-FF1C-CBCA-B96FFAF96158}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AD3D51C-CDED-5094-93B8-2B9454579E4A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2910,7 +1276,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2924,8 +1290,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="559443" y="10272532"/>
-          <a:ext cx="3165909" cy="2035216"/>
+          <a:off x="0" y="15154416"/>
+          <a:ext cx="3725916" cy="2372544"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2947,22 +1313,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>819873</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>115748</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>67191</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>771645</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>133650</xdr:rowOff>
+      <xdr:colOff>526980</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>52550</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7">
+        <xdr:cNvPr id="11" name="Picture 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F816F09D-06B3-F3D7-A37A-227A759A2A5D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5EB757D-0008-5905-0190-2C8439B26573}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2971,7 +1337,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2985,8 +1351,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="819873" y="12645343"/>
-          <a:ext cx="3163747" cy="2033826"/>
+          <a:off x="0" y="10220184"/>
+          <a:ext cx="3727380" cy="2376463"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3007,23 +1373,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>843644</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>23054</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>421822</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>166366</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>515007</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>1102</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
+        <xdr:cNvPr id="12" name="Picture 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AD3D51C-CDED-5094-93B8-2B9454579E4A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B4A4DF5-FA04-8EFE-065E-A4238D61A186}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3046,8 +1412,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4027715" y="5334000"/>
-          <a:ext cx="3823607" cy="2357116"/>
+          <a:off x="0" y="7784944"/>
+          <a:ext cx="3715407" cy="2369151"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3068,23 +1434,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1055914</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>119743</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>52646</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>487835</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>87086</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>525517</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>33950</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10">
+        <xdr:cNvPr id="14" name="Picture 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5EB757D-0008-5905-0190-2C8439B26573}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9287A982-0DEC-271E-7F97-CF0C0D8A9EEC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3107,8 +1473,72 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4256314" y="8338457"/>
-          <a:ext cx="3699121" cy="2373086"/>
+          <a:off x="0" y="17562880"/>
+          <a:ext cx="3725917" cy="2372408"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>899763</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>8283</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>949383</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>151143</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8805902F-0DBA-4423-9F2F-92A1181B9363}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="13701363" y="8283"/>
+          <a:ext cx="1116420" cy="333360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3129,23 +1559,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>950452</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>122903</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>49279</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>688258</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>101684</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>244929</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>117940</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 11">
+        <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B4A4DF5-FA04-8EFE-065E-A4238D61A186}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3D21546-12EE-544F-5F11-554B453A5161}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3154,7 +1584,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3168,8 +1598,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8406581" y="5407742"/>
-          <a:ext cx="3998451" cy="2502394"/>
+          <a:off x="0" y="5223259"/>
+          <a:ext cx="5578929" cy="3360501"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3190,23 +1620,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>56223</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>152491</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>85830</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>864124</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>129668</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>246184</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>106767</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 13">
+        <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9287A982-0DEC-271E-7F97-CF0C0D8A9EEC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{940D857F-4C4B-E054-2D54-B5321EE4CFDE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3215,7 +1645,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3229,8 +1659,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8603192" y="8157419"/>
-          <a:ext cx="4013014" cy="2506703"/>
+          <a:off x="0" y="12342307"/>
+          <a:ext cx="5580184" cy="3291675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3251,23 +1681,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>22194</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>59184</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>55898</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>606056</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>81378</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>240323</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>109391</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 14">
+        <xdr:cNvPr id="10" name="Picture 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F62A0426-C0F7-1F6D-2293-E874D0622B4A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D890A11-7872-D678-9967-F1AA3B3C9338}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3276,7 +1706,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3290,8 +1720,69 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4283476" y="10838155"/>
-          <a:ext cx="3779823" cy="2426563"/>
+          <a:off x="0" y="8678221"/>
+          <a:ext cx="5574323" cy="3505939"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>112207</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>257908</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>53361</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2277352C-5779-7812-CA33-1421885C0995}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="15821130"/>
+          <a:ext cx="5591908" cy="3575308"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3621,35 +2112,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="80"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="65"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="81" t="s">
+      <c r="I1" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="84" t="s">
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="85"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="78">
+      <c r="B2" s="63">
         <v>111222</v>
       </c>
-      <c r="C2" s="80"/>
+      <c r="C2" s="65"/>
       <c r="D2" s="40" t="s">
         <v>42</v>
       </c>
@@ -3665,15 +2156,15 @@
       <c r="J2" s="36">
         <v>45379</v>
       </c>
-      <c r="K2" s="88" t="s">
+      <c r="K2" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="89"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="87"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="81"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="66" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="38" t="s">
@@ -3691,21 +2182,21 @@
       <c r="F3" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="69"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="86"/>
     </row>
     <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="62"/>
+      <c r="A4" s="67"/>
       <c r="B4" s="11" t="s">
         <v>13</v>
       </c>
@@ -3721,19 +2212,19 @@
       <c r="F4" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="65"/>
-      <c r="H4" s="70" t="s">
+      <c r="G4" s="70"/>
+      <c r="H4" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="72"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="74"/>
     </row>
     <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63"/>
+      <c r="A5" s="68"/>
       <c r="B5" s="17">
         <v>0.6</v>
       </c>
@@ -3749,14 +2240,14 @@
       <c r="F5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="66"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="75"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="77"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
@@ -4213,17 +2704,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H5:N5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:N2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="H5:N5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4231,71 +2722,73 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D86138A-D68D-4D53-85AF-89D52F5F7A0B}">
-  <dimension ref="A1:Y86"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C834AC2-F2BD-4E29-9288-A591CBA1F41A}">
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="15.5546875" style="2" customWidth="1"/>
     <col min="6" max="10" width="15.5546875" style="1" customWidth="1"/>
     <col min="11" max="15" width="15.5546875" style="2" customWidth="1"/>
     <col min="16" max="20" width="14.33203125" style="2" customWidth="1"/>
-    <col min="21" max="25" width="8.88671875" style="2"/>
+    <col min="21" max="25" width="9.109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="80"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="63" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="65"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="90" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" s="91"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="84" t="s">
+      <c r="I1" s="87" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="85"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="78">
-        <v>112233</v>
-      </c>
-      <c r="C2" s="80"/>
+      <c r="B2" s="63">
+        <v>111222</v>
+      </c>
+      <c r="C2" s="65"/>
       <c r="D2" s="40" t="s">
         <v>42</v>
       </c>
       <c r="E2" s="41">
-        <v>45379</v>
+        <v>45376</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
+      <c r="I2" s="59" t="s">
+        <v>42</v>
+      </c>
       <c r="J2" s="36">
-        <v>45376</v>
-      </c>
-      <c r="K2" s="88" t="s">
+        <v>45379</v>
+      </c>
+      <c r="K2" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="89"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="87"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="81"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="61" t="s">
+      <c r="A3" s="66" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="38" t="s">
@@ -4310,22 +2803,24 @@
       <c r="E3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="64" t="s">
+      <c r="F3" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="69"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="86"/>
     </row>
     <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="62"/>
+      <c r="A4" s="67"/>
       <c r="B4" s="11" t="s">
         <v>13</v>
       </c>
@@ -4338,18 +2833,22 @@
       <c r="E4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="72"/>
+      <c r="F4" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="70"/>
+      <c r="H4" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="74"/>
     </row>
     <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63"/>
+      <c r="A5" s="68"/>
       <c r="B5" s="17">
         <v>0.6</v>
       </c>
@@ -4362,15 +2861,17 @@
       <c r="E5" s="18">
         <v>0.6</v>
       </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="75"/>
+      <c r="F5" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="71"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="77"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
@@ -4540,6 +3041,932 @@
       <c r="A11" s="22">
         <v>192</v>
       </c>
+      <c r="B11" s="50">
+        <v>0.38</v>
+      </c>
+      <c r="C11" s="23">
+        <f>A11*(B11+B5)</f>
+        <v>188.16</v>
+      </c>
+      <c r="D11" s="23">
+        <v>0.23</v>
+      </c>
+      <c r="E11" s="23">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="F11" s="24">
+        <f>(D11+E11)*9.81</f>
+        <v>5.1502500000000007</v>
+      </c>
+      <c r="G11" s="24">
+        <v>1442</v>
+      </c>
+      <c r="H11" s="24">
+        <f>F11*E5</f>
+        <v>3.0901500000000004</v>
+      </c>
+      <c r="I11" s="24">
+        <f>H11*0.035</f>
+        <v>0.10815525000000002</v>
+      </c>
+      <c r="J11" s="24">
+        <f>(2*3.14*G11*I11)/60</f>
+        <v>16.323799779000005</v>
+      </c>
+      <c r="K11" s="24">
+        <v>0</v>
+      </c>
+      <c r="L11" s="24">
+        <v>1</v>
+      </c>
+      <c r="M11" s="23">
+        <f>(J11*L11)/C11</f>
+        <v>8.6754888281250025E-2</v>
+      </c>
+      <c r="N11" s="25">
+        <f>M11*100</f>
+        <v>8.6754888281250029</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="26">
+        <v>192</v>
+      </c>
+      <c r="B12" s="51">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C12" s="27">
+        <f>A11*(B12+B5)</f>
+        <v>220.79999999999998</v>
+      </c>
+      <c r="D12" s="27">
+        <v>0.47</v>
+      </c>
+      <c r="E12" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="F12" s="24">
+        <f>(D12+E12)*9.81</f>
+        <v>10.496699999999999</v>
+      </c>
+      <c r="G12" s="20">
+        <v>1432</v>
+      </c>
+      <c r="H12" s="20">
+        <f>F12*E5</f>
+        <v>6.2980199999999993</v>
+      </c>
+      <c r="I12" s="24">
+        <f t="shared" ref="I12:I18" si="0">H12*0.035</f>
+        <v>0.22043070000000001</v>
+      </c>
+      <c r="J12" s="24">
+        <f t="shared" ref="J12:J18" si="1">(2*3.14*G12*I12)/60</f>
+        <v>33.038741131200005</v>
+      </c>
+      <c r="K12" s="20">
+        <v>0</v>
+      </c>
+      <c r="L12" s="20">
+        <v>1</v>
+      </c>
+      <c r="M12" s="23">
+        <f t="shared" ref="M12:M18" si="2">(J12*L12)/C12</f>
+        <v>0.14963197976086959</v>
+      </c>
+      <c r="N12" s="25">
+        <f t="shared" ref="N12:N18" si="3">M12*100</f>
+        <v>14.963197976086958</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="29">
+        <v>192</v>
+      </c>
+      <c r="B13" s="52">
+        <v>0.65</v>
+      </c>
+      <c r="C13" s="30">
+        <f>A11*(B13+B5)</f>
+        <v>240</v>
+      </c>
+      <c r="D13" s="30">
+        <v>0.71</v>
+      </c>
+      <c r="E13" s="30">
+        <v>0.82</v>
+      </c>
+      <c r="F13" s="54">
+        <f t="shared" ref="F13:F18" si="4">(D13+E13)*9.81</f>
+        <v>15.0093</v>
+      </c>
+      <c r="G13" s="31">
+        <v>1450</v>
+      </c>
+      <c r="H13" s="31">
+        <f>F13*E5</f>
+        <v>9.0055800000000001</v>
+      </c>
+      <c r="I13" s="54">
+        <f t="shared" si="0"/>
+        <v>0.31519530000000001</v>
+      </c>
+      <c r="J13" s="54">
+        <f t="shared" si="1"/>
+        <v>47.836140030000003</v>
+      </c>
+      <c r="K13" s="31">
+        <v>0</v>
+      </c>
+      <c r="L13" s="31">
+        <v>1</v>
+      </c>
+      <c r="M13" s="56">
+        <f t="shared" si="2"/>
+        <v>0.19931725012500001</v>
+      </c>
+      <c r="N13" s="57">
+        <f t="shared" si="3"/>
+        <v>19.931725012500003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="29">
+        <v>192</v>
+      </c>
+      <c r="B14" s="52">
+        <v>0.8</v>
+      </c>
+      <c r="C14" s="30">
+        <f>A11*(B14+B5)</f>
+        <v>268.79999999999995</v>
+      </c>
+      <c r="D14" s="30">
+        <v>0.93499999999999994</v>
+      </c>
+      <c r="E14" s="30">
+        <v>1.0649999999999999</v>
+      </c>
+      <c r="F14" s="54">
+        <f t="shared" si="4"/>
+        <v>19.62</v>
+      </c>
+      <c r="G14" s="31">
+        <v>1432</v>
+      </c>
+      <c r="H14" s="31">
+        <f>F14*E5</f>
+        <v>11.772</v>
+      </c>
+      <c r="I14" s="54">
+        <f t="shared" si="0"/>
+        <v>0.41202000000000005</v>
+      </c>
+      <c r="J14" s="54">
+        <f t="shared" si="1"/>
+        <v>61.754656320000009</v>
+      </c>
+      <c r="K14" s="31">
+        <v>0</v>
+      </c>
+      <c r="L14" s="31">
+        <v>1</v>
+      </c>
+      <c r="M14" s="56">
+        <f t="shared" si="2"/>
+        <v>0.22974202500000007</v>
+      </c>
+      <c r="N14" s="57">
+        <f t="shared" si="3"/>
+        <v>22.974202500000008</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="26">
+        <v>192</v>
+      </c>
+      <c r="B15" s="51">
+        <v>1</v>
+      </c>
+      <c r="C15" s="27">
+        <f>A11*(B15+B5)</f>
+        <v>307.20000000000005</v>
+      </c>
+      <c r="D15" s="27">
+        <v>1.2249999999999999</v>
+      </c>
+      <c r="E15" s="27">
+        <v>1.4449999999999998</v>
+      </c>
+      <c r="F15" s="24">
+        <f t="shared" si="4"/>
+        <v>26.192700000000002</v>
+      </c>
+      <c r="G15" s="20">
+        <v>1400</v>
+      </c>
+      <c r="H15" s="20">
+        <f>F15*E5</f>
+        <v>15.715620000000001</v>
+      </c>
+      <c r="I15" s="24">
+        <f t="shared" si="0"/>
+        <v>0.55004670000000011</v>
+      </c>
+      <c r="J15" s="24">
+        <f t="shared" si="1"/>
+        <v>80.600176440000013</v>
+      </c>
+      <c r="K15" s="20">
+        <v>0</v>
+      </c>
+      <c r="L15" s="20">
+        <v>1</v>
+      </c>
+      <c r="M15" s="23">
+        <f t="shared" si="2"/>
+        <v>0.26237036601562502</v>
+      </c>
+      <c r="N15" s="25">
+        <f t="shared" si="3"/>
+        <v>26.237036601562501</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="26">
+        <v>192</v>
+      </c>
+      <c r="B16" s="51">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C16" s="27">
+        <f>A11*(B16+B5)</f>
+        <v>330.24</v>
+      </c>
+      <c r="D16" s="27">
+        <v>1.5099999999999998</v>
+      </c>
+      <c r="E16" s="27">
+        <v>1.8049999999999997</v>
+      </c>
+      <c r="F16" s="24">
+        <f t="shared" si="4"/>
+        <v>32.520149999999994</v>
+      </c>
+      <c r="G16" s="20">
+        <v>1394</v>
+      </c>
+      <c r="H16" s="20">
+        <f>F16*E5</f>
+        <v>19.512089999999997</v>
+      </c>
+      <c r="I16" s="24">
+        <f t="shared" si="0"/>
+        <v>0.68292314999999992</v>
+      </c>
+      <c r="J16" s="24">
+        <f t="shared" si="1"/>
+        <v>99.642129841799985</v>
+      </c>
+      <c r="K16" s="20">
+        <v>0</v>
+      </c>
+      <c r="L16" s="20">
+        <v>1</v>
+      </c>
+      <c r="M16" s="23">
+        <f t="shared" si="2"/>
+        <v>0.30172641061591565</v>
+      </c>
+      <c r="N16" s="25">
+        <f t="shared" si="3"/>
+        <v>30.172641061591566</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="29">
+        <v>192</v>
+      </c>
+      <c r="B17" s="52">
+        <v>1.3</v>
+      </c>
+      <c r="C17" s="30">
+        <f>A11*(B17+B5)</f>
+        <v>364.79999999999995</v>
+      </c>
+      <c r="D17" s="30">
+        <v>1.8149999999999997</v>
+      </c>
+      <c r="E17" s="30">
+        <v>2.4249999999999998</v>
+      </c>
+      <c r="F17" s="54">
+        <f t="shared" si="4"/>
+        <v>41.594399999999993</v>
+      </c>
+      <c r="G17" s="31">
+        <v>1354</v>
+      </c>
+      <c r="H17" s="31">
+        <f>F17*E5</f>
+        <v>24.956639999999997</v>
+      </c>
+      <c r="I17" s="54">
+        <f t="shared" si="0"/>
+        <v>0.87348239999999999</v>
+      </c>
+      <c r="J17" s="54">
+        <f t="shared" si="1"/>
+        <v>123.7887610848</v>
+      </c>
+      <c r="K17" s="31">
+        <v>0</v>
+      </c>
+      <c r="L17" s="31">
+        <v>1</v>
+      </c>
+      <c r="M17" s="56">
+        <f t="shared" si="2"/>
+        <v>0.33933322665789478</v>
+      </c>
+      <c r="N17" s="57">
+        <f t="shared" si="3"/>
+        <v>33.933322665789476</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="29">
+        <v>192</v>
+      </c>
+      <c r="B18" s="52">
+        <v>1.7</v>
+      </c>
+      <c r="C18" s="30">
+        <f>A11*(B18+B5)</f>
+        <v>441.59999999999997</v>
+      </c>
+      <c r="D18" s="30">
+        <v>1.8999999999999997</v>
+      </c>
+      <c r="E18" s="30">
+        <v>2.4449999999999998</v>
+      </c>
+      <c r="F18" s="54">
+        <f t="shared" si="4"/>
+        <v>42.624450000000003</v>
+      </c>
+      <c r="G18" s="31">
+        <v>1352</v>
+      </c>
+      <c r="H18" s="31">
+        <f>F18*E5</f>
+        <v>25.574670000000001</v>
+      </c>
+      <c r="I18" s="54">
+        <f t="shared" si="0"/>
+        <v>0.89511345000000009</v>
+      </c>
+      <c r="J18" s="54">
+        <f t="shared" si="1"/>
+        <v>126.66690756720001</v>
+      </c>
+      <c r="K18" s="31">
+        <v>0</v>
+      </c>
+      <c r="L18" s="31">
+        <v>1</v>
+      </c>
+      <c r="M18" s="56">
+        <f t="shared" si="2"/>
+        <v>0.28683629430978264</v>
+      </c>
+      <c r="N18" s="57">
+        <f t="shared" si="3"/>
+        <v>28.683629430978264</v>
+      </c>
+      <c r="P18"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="25"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="25"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="29"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="32"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="32"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="28"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="28"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="32"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="32"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="28"/>
+    </row>
+    <row r="28" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="33"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="35"/>
+    </row>
+    <row r="37" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C37"/>
+    </row>
+    <row r="38" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="F38"/>
+    </row>
+    <row r="45" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="F45"/>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C49"/>
+      <c r="J49"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="J51"/>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F52"/>
+      <c r="K52"/>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B61"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F64"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B74"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B75"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="M1:N2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="G3:G5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D86138A-D68D-4D53-85AF-89D52F5F7A0B}">
+  <dimension ref="A1:Y86"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="5" width="15.5546875" style="2" customWidth="1"/>
+    <col min="6" max="10" width="15.5546875" style="1" customWidth="1"/>
+    <col min="11" max="15" width="15.5546875" style="2" customWidth="1"/>
+    <col min="16" max="20" width="14.33203125" style="2" customWidth="1"/>
+    <col min="21" max="25" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="91"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="79"/>
+    </row>
+    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="63">
+        <v>112233</v>
+      </c>
+      <c r="C2" s="65"/>
+      <c r="D2" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="41">
+        <v>45379</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="36">
+        <v>45376</v>
+      </c>
+      <c r="K2" s="82" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="83"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="81"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="86"/>
+    </row>
+    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="67"/>
+      <c r="B4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="13"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="74"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="68"/>
+      <c r="B5" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="C5" s="18">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D5" s="18">
+        <v>9.81</v>
+      </c>
+      <c r="E5" s="18">
+        <v>0.6</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="77"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" s="45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="22">
+        <v>192</v>
+      </c>
       <c r="B11" s="46">
         <v>0.35</v>
       </c>
@@ -5195,953 +4622,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="H5:N5"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="J1:L1"/>
     <mergeCell ref="M1:N2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="K2:L2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C834AC2-F2BD-4E29-9288-A591CBA1F41A}">
-  <dimension ref="A1:Y75"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="5" width="15.5546875" style="2" customWidth="1"/>
-    <col min="6" max="10" width="15.5546875" style="1" customWidth="1"/>
-    <col min="11" max="15" width="15.5546875" style="2" customWidth="1"/>
-    <col min="16" max="20" width="14.33203125" style="2" customWidth="1"/>
-    <col min="21" max="25" width="9.109375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="81" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="84" t="s">
-        <v>37</v>
-      </c>
-      <c r="N1" s="85"/>
-    </row>
-    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="78">
-        <v>111222</v>
-      </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="41">
-        <v>45376</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="36">
-        <v>45379</v>
-      </c>
-      <c r="K2" s="88" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="89"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="87"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="61" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="60" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="69"/>
-    </row>
-    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="62"/>
-      <c r="B4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="65"/>
-      <c r="H4" s="70" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="72"/>
-    </row>
-    <row r="5" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63"/>
-      <c r="B5" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="C5" s="18">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="D5" s="18">
-        <v>9.81</v>
-      </c>
-      <c r="E5" s="18">
-        <v>0.6</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="66"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="75"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="N10" s="45" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
-        <v>192</v>
-      </c>
-      <c r="B11" s="50">
-        <v>0.38</v>
-      </c>
-      <c r="C11" s="23">
-        <f>A11*(B11+B5)</f>
-        <v>188.16</v>
-      </c>
-      <c r="D11" s="23">
-        <v>0.23</v>
-      </c>
-      <c r="E11" s="23">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="F11" s="24">
-        <f>(D11+E11)*9.81</f>
-        <v>5.1502500000000007</v>
-      </c>
-      <c r="G11" s="24">
-        <v>1442</v>
-      </c>
-      <c r="H11" s="24">
-        <f>F11*E5</f>
-        <v>3.0901500000000004</v>
-      </c>
-      <c r="I11" s="24">
-        <f>H11*0.035</f>
-        <v>0.10815525000000002</v>
-      </c>
-      <c r="J11" s="24">
-        <f>(2*3.14*G11*I11)/60</f>
-        <v>16.323799779000005</v>
-      </c>
-      <c r="K11" s="24">
-        <v>0</v>
-      </c>
-      <c r="L11" s="24">
-        <v>1</v>
-      </c>
-      <c r="M11" s="23">
-        <f>(J11*L11)/C11</f>
-        <v>8.6754888281250025E-2</v>
-      </c>
-      <c r="N11" s="25">
-        <f>M11*100</f>
-        <v>8.6754888281250029</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="26">
-        <v>192</v>
-      </c>
-      <c r="B12" s="51">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C12" s="27">
-        <f>A11*(B12+B5)</f>
-        <v>220.79999999999998</v>
-      </c>
-      <c r="D12" s="27">
-        <v>0.47</v>
-      </c>
-      <c r="E12" s="27">
-        <v>0.6</v>
-      </c>
-      <c r="F12" s="24">
-        <f>(D12+E12)*9.81</f>
-        <v>10.496699999999999</v>
-      </c>
-      <c r="G12" s="20">
-        <v>1432</v>
-      </c>
-      <c r="H12" s="20">
-        <f>F12*E5</f>
-        <v>6.2980199999999993</v>
-      </c>
-      <c r="I12" s="24">
-        <f t="shared" ref="I12:I18" si="0">H12*0.035</f>
-        <v>0.22043070000000001</v>
-      </c>
-      <c r="J12" s="24">
-        <f t="shared" ref="J12:J18" si="1">(2*3.14*G12*I12)/60</f>
-        <v>33.038741131200005</v>
-      </c>
-      <c r="K12" s="20">
-        <v>0</v>
-      </c>
-      <c r="L12" s="20">
-        <v>1</v>
-      </c>
-      <c r="M12" s="23">
-        <f t="shared" ref="M12:M18" si="2">(J12*L12)/C12</f>
-        <v>0.14963197976086959</v>
-      </c>
-      <c r="N12" s="25">
-        <f t="shared" ref="N12:N18" si="3">M12*100</f>
-        <v>14.963197976086958</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="29">
-        <v>192</v>
-      </c>
-      <c r="B13" s="52">
-        <v>0.65</v>
-      </c>
-      <c r="C13" s="30">
-        <f>A11*(B13+B5)</f>
-        <v>240</v>
-      </c>
-      <c r="D13" s="30">
-        <v>0.71</v>
-      </c>
-      <c r="E13" s="30">
-        <v>0.82</v>
-      </c>
-      <c r="F13" s="54">
-        <f t="shared" ref="F13:F18" si="4">(D13+E13)*9.81</f>
-        <v>15.0093</v>
-      </c>
-      <c r="G13" s="31">
-        <v>1450</v>
-      </c>
-      <c r="H13" s="31">
-        <f>F13*E5</f>
-        <v>9.0055800000000001</v>
-      </c>
-      <c r="I13" s="54">
-        <f t="shared" si="0"/>
-        <v>0.31519530000000001</v>
-      </c>
-      <c r="J13" s="54">
-        <f t="shared" si="1"/>
-        <v>47.836140030000003</v>
-      </c>
-      <c r="K13" s="31">
-        <v>0</v>
-      </c>
-      <c r="L13" s="31">
-        <v>1</v>
-      </c>
-      <c r="M13" s="56">
-        <f t="shared" si="2"/>
-        <v>0.19931725012500001</v>
-      </c>
-      <c r="N13" s="57">
-        <f t="shared" si="3"/>
-        <v>19.931725012500003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="29">
-        <v>192</v>
-      </c>
-      <c r="B14" s="52">
-        <v>0.8</v>
-      </c>
-      <c r="C14" s="30">
-        <f>A11*(B14+B5)</f>
-        <v>268.79999999999995</v>
-      </c>
-      <c r="D14" s="30">
-        <v>0.93499999999999994</v>
-      </c>
-      <c r="E14" s="30">
-        <v>1.0649999999999999</v>
-      </c>
-      <c r="F14" s="54">
-        <f t="shared" si="4"/>
-        <v>19.62</v>
-      </c>
-      <c r="G14" s="31">
-        <v>1432</v>
-      </c>
-      <c r="H14" s="31">
-        <f>F14*E5</f>
-        <v>11.772</v>
-      </c>
-      <c r="I14" s="54">
-        <f t="shared" si="0"/>
-        <v>0.41202000000000005</v>
-      </c>
-      <c r="J14" s="54">
-        <f t="shared" si="1"/>
-        <v>61.754656320000009</v>
-      </c>
-      <c r="K14" s="31">
-        <v>0</v>
-      </c>
-      <c r="L14" s="31">
-        <v>1</v>
-      </c>
-      <c r="M14" s="56">
-        <f t="shared" si="2"/>
-        <v>0.22974202500000007</v>
-      </c>
-      <c r="N14" s="57">
-        <f t="shared" si="3"/>
-        <v>22.974202500000008</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="26">
-        <v>192</v>
-      </c>
-      <c r="B15" s="51">
-        <v>1</v>
-      </c>
-      <c r="C15" s="27">
-        <f>A11*(B15+B5)</f>
-        <v>307.20000000000005</v>
-      </c>
-      <c r="D15" s="27">
-        <v>1.2249999999999999</v>
-      </c>
-      <c r="E15" s="27">
-        <v>1.4449999999999998</v>
-      </c>
-      <c r="F15" s="24">
-        <f t="shared" si="4"/>
-        <v>26.192700000000002</v>
-      </c>
-      <c r="G15" s="20">
-        <v>1400</v>
-      </c>
-      <c r="H15" s="20">
-        <f>F15*E5</f>
-        <v>15.715620000000001</v>
-      </c>
-      <c r="I15" s="24">
-        <f t="shared" si="0"/>
-        <v>0.55004670000000011</v>
-      </c>
-      <c r="J15" s="24">
-        <f t="shared" si="1"/>
-        <v>80.600176440000013</v>
-      </c>
-      <c r="K15" s="20">
-        <v>0</v>
-      </c>
-      <c r="L15" s="20">
-        <v>1</v>
-      </c>
-      <c r="M15" s="23">
-        <f t="shared" si="2"/>
-        <v>0.26237036601562502</v>
-      </c>
-      <c r="N15" s="25">
-        <f t="shared" si="3"/>
-        <v>26.237036601562501</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="26">
-        <v>192</v>
-      </c>
-      <c r="B16" s="51">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="C16" s="27">
-        <f>A11*(B16+B5)</f>
-        <v>330.24</v>
-      </c>
-      <c r="D16" s="27">
-        <v>1.5099999999999998</v>
-      </c>
-      <c r="E16" s="27">
-        <v>1.8049999999999997</v>
-      </c>
-      <c r="F16" s="24">
-        <f t="shared" si="4"/>
-        <v>32.520149999999994</v>
-      </c>
-      <c r="G16" s="20">
-        <v>1394</v>
-      </c>
-      <c r="H16" s="20">
-        <f>F16*E5</f>
-        <v>19.512089999999997</v>
-      </c>
-      <c r="I16" s="24">
-        <f t="shared" si="0"/>
-        <v>0.68292314999999992</v>
-      </c>
-      <c r="J16" s="24">
-        <f t="shared" si="1"/>
-        <v>99.642129841799985</v>
-      </c>
-      <c r="K16" s="20">
-        <v>0</v>
-      </c>
-      <c r="L16" s="20">
-        <v>1</v>
-      </c>
-      <c r="M16" s="23">
-        <f t="shared" si="2"/>
-        <v>0.30172641061591565</v>
-      </c>
-      <c r="N16" s="25">
-        <f t="shared" si="3"/>
-        <v>30.172641061591566</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="29">
-        <v>192</v>
-      </c>
-      <c r="B17" s="52">
-        <v>1.3</v>
-      </c>
-      <c r="C17" s="30">
-        <f>A11*(B17+B5)</f>
-        <v>364.79999999999995</v>
-      </c>
-      <c r="D17" s="30">
-        <v>1.8149999999999997</v>
-      </c>
-      <c r="E17" s="30">
-        <v>2.4249999999999998</v>
-      </c>
-      <c r="F17" s="54">
-        <f t="shared" si="4"/>
-        <v>41.594399999999993</v>
-      </c>
-      <c r="G17" s="31">
-        <v>1354</v>
-      </c>
-      <c r="H17" s="31">
-        <f>F17*E5</f>
-        <v>24.956639999999997</v>
-      </c>
-      <c r="I17" s="54">
-        <f t="shared" si="0"/>
-        <v>0.87348239999999999</v>
-      </c>
-      <c r="J17" s="54">
-        <f t="shared" si="1"/>
-        <v>123.7887610848</v>
-      </c>
-      <c r="K17" s="31">
-        <v>0</v>
-      </c>
-      <c r="L17" s="31">
-        <v>1</v>
-      </c>
-      <c r="M17" s="56">
-        <f t="shared" si="2"/>
-        <v>0.33933322665789478</v>
-      </c>
-      <c r="N17" s="57">
-        <f t="shared" si="3"/>
-        <v>33.933322665789476</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="29">
-        <v>192</v>
-      </c>
-      <c r="B18" s="52">
-        <v>1.7</v>
-      </c>
-      <c r="C18" s="30">
-        <f>A11*(B18+B5)</f>
-        <v>441.59999999999997</v>
-      </c>
-      <c r="D18" s="30">
-        <v>1.8999999999999997</v>
-      </c>
-      <c r="E18" s="30">
-        <v>2.4449999999999998</v>
-      </c>
-      <c r="F18" s="54">
-        <f t="shared" si="4"/>
-        <v>42.624450000000003</v>
-      </c>
-      <c r="G18" s="31">
-        <v>1352</v>
-      </c>
-      <c r="H18" s="31">
-        <f>F18*E5</f>
-        <v>25.574670000000001</v>
-      </c>
-      <c r="I18" s="54">
-        <f t="shared" si="0"/>
-        <v>0.89511345000000009</v>
-      </c>
-      <c r="J18" s="54">
-        <f t="shared" si="1"/>
-        <v>126.66690756720001</v>
-      </c>
-      <c r="K18" s="31">
-        <v>0</v>
-      </c>
-      <c r="L18" s="31">
-        <v>1</v>
-      </c>
-      <c r="M18" s="56">
-        <f t="shared" si="2"/>
-        <v>0.28683629430978264</v>
-      </c>
-      <c r="N18" s="57">
-        <f t="shared" si="3"/>
-        <v>28.683629430978264</v>
-      </c>
-      <c r="P18"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="25"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="25"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="29"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="32"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="29"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="32"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="28"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="28"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="29"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="32"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="29"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="32"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="28"/>
-    </row>
-    <row r="28" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="33"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="35"/>
-    </row>
-    <row r="37" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C37"/>
-    </row>
-    <row r="38" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="F38"/>
-    </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="F45"/>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C49"/>
-      <c r="J49"/>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="J51"/>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="F52"/>
-      <c r="K52"/>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B61"/>
-    </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="F64"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B74"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B75"/>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="B2:C2"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:N3"/>
     <mergeCell ref="H4:N4"/>
     <mergeCell ref="H5:N5"/>
-    <mergeCell ref="M1:N2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="H3:N3"/>
-    <mergeCell ref="I1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
